--- a/data/trans_bre/P57_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P57_R-Provincia-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 8,8</t>
+          <t>-7,25; 9,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 4,04</t>
+          <t>-2,87; 4,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 34,01</t>
+          <t>-21,46; 37,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-36,26; 107,07</t>
+          <t>-37,73; 108,73</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 4,64</t>
+          <t>-3,97; 5,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,47</t>
+          <t>-2,67; 3,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-28,89; 38,01</t>
+          <t>-23,78; 43,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 94,06</t>
+          <t>-36,82; 87,31</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 12,4</t>
+          <t>2,3; 12,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 6,57</t>
+          <t>-4,17; 6,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,23; 201,88</t>
+          <t>17,45; 188,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 39,1</t>
+          <t>-18,47; 39,03</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 18,38</t>
+          <t>5,68; 18,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 2,61</t>
+          <t>-8,54; 2,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,2; 141,45</t>
+          <t>29,03; 146,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,73; 25,46</t>
+          <t>-54,08; 28,23</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 15,65</t>
+          <t>-1,71; 15,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 5,73</t>
+          <t>-1,94; 5,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 52,34</t>
+          <t>-4,42; 55,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 111,27</t>
+          <t>-20,79; 114,07</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 9,79</t>
+          <t>-4,34; 9,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 6,86</t>
+          <t>-4,04; 7,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 65,07</t>
+          <t>-20,85; 58,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 38,69</t>
+          <t>-16,89; 44,42</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 8,82</t>
+          <t>-0,22; 8,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 4,92</t>
+          <t>-5,09; 5,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 65,03</t>
+          <t>-1,87; 62,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-57,58; 60,65</t>
+          <t>-45,58; 60,43</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,74</t>
+          <t>1,74; 10,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,44; 27,67</t>
+          <t>10,01; 27,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,62; 56,3</t>
+          <t>7,71; 59,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44,04; 363,48</t>
+          <t>42,57; 327,99</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,96</t>
+          <t>2,9; 6,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 6,42</t>
+          <t>0,23; 6,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14,74; 39,33</t>
+          <t>15,13; 40,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,75; 63,47</t>
+          <t>3,27; 61,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P57_R-Provincia-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 9,24</t>
+          <t>-6,26; 8,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 4,0</t>
+          <t>-2,04; 3,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,46; 37,92</t>
+          <t>-18,38; 32,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-37,73; 108,73</t>
+          <t>-28,44; 94,49</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 5,12</t>
+          <t>-3,95; 5,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 3,24</t>
+          <t>-2,69; 3,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 43,86</t>
+          <t>-24,46; 48,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 87,31</t>
+          <t>-35,78; 85,12</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,27</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 12,39</t>
+          <t>1,78; 12,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 6,38</t>
+          <t>-5,09; 5,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,45; 188,65</t>
+          <t>17,72; 188,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 39,03</t>
+          <t>-21,19; 30,28</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-19,9%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 18,41</t>
+          <t>5,48; 18,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 2,86</t>
+          <t>-5,09; 5,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,03; 146,47</t>
+          <t>29,35; 139,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,08; 28,23</t>
+          <t>-32,97; 62,42</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 15,85</t>
+          <t>-1,66; 15,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 5,51</t>
+          <t>-2,71; 4,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 55,06</t>
+          <t>-4,03; 53,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 114,07</t>
+          <t>-28,2; 94,84</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 9,26</t>
+          <t>-4,23; 10,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 7,94</t>
+          <t>-4,69; 6,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 58,47</t>
+          <t>-18,96; 68,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 44,42</t>
+          <t>-18,63; 35,01</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>3,75</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 8,9</t>
+          <t>0,22; 9,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 5,19</t>
+          <t>0,33; 6,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 62,51</t>
+          <t>1,13; 64,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-45,58; 60,43</t>
+          <t>3,57; 91,72</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17,5</t>
+          <t>12,33</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>104,32%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,74; 10,41</t>
+          <t>1,24; 10,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,01; 27,31</t>
+          <t>8,71; 16,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,71; 59,94</t>
+          <t>5,86; 57,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42,57; 327,99</t>
+          <t>37,38; 86,23</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,99</t>
+          <t>2,83; 6,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,25</t>
+          <t>2,31; 5,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,13; 40,28</t>
+          <t>14,91; 40,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,27; 61,0</t>
+          <t>15,92; 41,97</t>
         </is>
       </c>
     </row>
